--- a/A310/A320.xlsx
+++ b/A310/A320.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMART\Desktop\폴리텍실습\python\A310\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F4F57B-F2D4-4CCE-8CBC-56058A5B541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A535831F-2702-418D-83EA-C96715CA827B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-24" windowWidth="23256" windowHeight="12456" xr2:uid="{BF37FDD5-EF12-4412-9021-9692EA782CD6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BF37FDD5-EF12-4412-9021-9692EA782CD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>학생이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -189,6 +211,18 @@
   </si>
   <si>
     <t>이씨이면서 과제등급이 B 또는 C인 합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUMPRODUCT((B3:B22="A")+(B3:B22="B"),H3:H22)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=SUMPRODUCT((LEFT($A$3:$A$22)="이")*(($B$3:$B$22="B")+($B$3:$B$22="C")),G3:G22)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -196,7 +230,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +246,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -221,12 +262,90 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -235,11 +354,53 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -257,6 +418,1232 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>학생별 성적현황</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>총점</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>송경관</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>송수정</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>송대관</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>신명훈</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>홍길동</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>박현정</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>김찬진</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>76.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76.800000000000011</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>83.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>76.800000000000011</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.400000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B0CE-442B-9626-DA1AD16D9886}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="1315522111"/>
+        <c:axId val="1314169871"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>조정점수</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>송경관</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>송수정</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>송대관</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>신명훈</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>홍길동</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>박현정</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>김찬진</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$3:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>18.400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.400000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B0CE-442B-9626-DA1AD16D9886}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1315522111"/>
+        <c:axId val="1314169871"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1315522111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US"/>
+                  <a:t>학생이름</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1314169871"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1314169871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US"/>
+                  <a:t>점수</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ko-KR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1315522111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9334BF4-C991-9736-4920-9134FEEEB9CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -556,342 +1943,853 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3CFF4-BE3D-4025-BFA4-F211636EDB10}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="25.2" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6">
+        <v>62</v>
+      </c>
+      <c r="D3" s="6">
+        <v>92</v>
+      </c>
+      <c r="E3" s="6">
+        <f>IF(B3="A",20,IF(B3="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F3" s="6">
+        <f>E3+(C3+D3)*40%</f>
+        <v>81.599999999999994</v>
+      </c>
+      <c r="G3" s="6">
+        <f>IF(D3&gt;=C3,D3*20%,C3*10%)</f>
+        <v>18.400000000000002</v>
+      </c>
+      <c r="H3" s="6">
+        <f>F3+G3</f>
+        <v>100</v>
+      </c>
+      <c r="I3" s="7">
+        <f>RANK(H3,$H$3:$H$22,)</f>
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="J3" s="5" t="str">
+        <f>IF(H3&gt;=90,"최우수",IF(H3&gt;=80,"우수",IF(H3&lt;60,"미달","보통")))</f>
+        <v>최우수</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="9">
+        <v>65</v>
+      </c>
+      <c r="D4" s="9">
+        <v>88</v>
+      </c>
+      <c r="E4" s="9">
+        <f>IF(B4="A",20,IF(B4="B",15,10))</f>
+        <v>15</v>
+      </c>
+      <c r="F4" s="9">
+        <f>E4+(C4+D4)*40%</f>
+        <v>76.2</v>
+      </c>
+      <c r="G4" s="9">
+        <f>IF(D4&gt;=C4,D4*20%,C4*10%)</f>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="H4" s="9">
+        <f>F4+G4</f>
+        <v>93.800000000000011</v>
+      </c>
+      <c r="I4" s="10">
+        <f>RANK(H4,$H$3:$H$22,)</f>
+        <v>2</v>
+      </c>
+      <c r="J4" s="8" t="str">
+        <f>IF(H4&gt;=90,"최우수",IF(H4&gt;=80,"우수",IF(H4&lt;60,"미달","보통")))</f>
+        <v>최우수</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="9">
+        <v>62</v>
+      </c>
+      <c r="D5" s="9">
+        <v>80</v>
+      </c>
+      <c r="E5" s="9">
+        <f>IF(B5="A",20,IF(B5="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F5" s="9">
+        <f>E5+(C5+D5)*40%</f>
+        <v>76.800000000000011</v>
+      </c>
+      <c r="G5" s="9">
+        <f>IF(D5&gt;=C5,D5*20%,C5*10%)</f>
+        <v>16</v>
+      </c>
+      <c r="H5" s="9">
+        <f>F5+G5</f>
+        <v>92.800000000000011</v>
+      </c>
+      <c r="I5" s="10">
+        <f>RANK(H5,$H$3:$H$22,)</f>
+        <v>3</v>
+      </c>
+      <c r="J5" s="8" t="str">
+        <f>IF(H5&gt;=90,"최우수",IF(H5&gt;=80,"우수",IF(H5&lt;60,"미달","보통")))</f>
+        <v>최우수</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="9">
+        <v>85</v>
+      </c>
+      <c r="D6" s="9">
+        <v>74</v>
+      </c>
+      <c r="E6" s="9">
+        <f>IF(B6="A",20,IF(B6="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F6" s="9">
+        <f>E6+(C6+D6)*40%</f>
+        <v>83.6</v>
+      </c>
+      <c r="G6" s="9">
+        <f>IF(D6&gt;=C6,D6*20%,C6*10%)</f>
+        <v>8.5</v>
+      </c>
+      <c r="H6" s="9">
+        <f>F6+G6</f>
+        <v>92.1</v>
+      </c>
+      <c r="I6" s="10">
+        <f>RANK(H6,$H$3:$H$22,)</f>
+        <v>4</v>
+      </c>
+      <c r="J6" s="8" t="str">
+        <f>IF(H6&gt;=90,"최우수",IF(H6&gt;=80,"우수",IF(H6&lt;60,"미달","보통")))</f>
+        <v>최우수</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9">
+        <v>70</v>
+      </c>
+      <c r="D7" s="9">
+        <v>72</v>
+      </c>
+      <c r="E7" s="9">
+        <f>IF(B7="A",20,IF(B7="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F7" s="9">
+        <f>E7+(C7+D7)*40%</f>
+        <v>76.800000000000011</v>
+      </c>
+      <c r="G7" s="9">
+        <f>IF(D7&gt;=C7,D7*20%,C7*10%)</f>
+        <v>14.4</v>
+      </c>
+      <c r="H7" s="9">
+        <f>F7+G7</f>
+        <v>91.200000000000017</v>
+      </c>
+      <c r="I7" s="10">
+        <f>RANK(H7,$H$3:$H$22,)</f>
+        <v>5</v>
+      </c>
+      <c r="J7" s="8" t="str">
+        <f>IF(H7&gt;=90,"최우수",IF(H7&gt;=80,"우수",IF(H7&lt;60,"미달","보통")))</f>
+        <v>최우수</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3">
+      <c r="C8" s="9">
+        <v>77</v>
+      </c>
+      <c r="D8" s="9">
+        <v>78</v>
+      </c>
+      <c r="E8" s="9">
+        <f>IF(B8="A",20,IF(B8="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F8" s="9">
+        <f>E8+(C8+D8)*40%</f>
+        <v>72</v>
+      </c>
+      <c r="G8" s="9">
+        <f>IF(D8&gt;=C8,D8*20%,C8*10%)</f>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="H8" s="9">
+        <f>F8+G8</f>
+        <v>87.6</v>
+      </c>
+      <c r="I8" s="10">
+        <f>RANK(H8,$H$3:$H$22,)</f>
+        <v>6</v>
+      </c>
+      <c r="J8" s="8" t="str">
+        <f>IF(H8&gt;=90,"최우수",IF(H8&gt;=80,"우수",IF(H8&lt;60,"미달","보통")))</f>
+        <v>우수</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="9">
+        <v>69</v>
+      </c>
+      <c r="D9" s="9">
+        <v>82</v>
+      </c>
+      <c r="E9" s="9">
+        <f>IF(B9="A",20,IF(B9="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F9" s="9">
+        <f>E9+(C9+D9)*40%</f>
+        <v>70.400000000000006</v>
+      </c>
+      <c r="G9" s="9">
+        <f>IF(D9&gt;=C9,D9*20%,C9*10%)</f>
+        <v>16.400000000000002</v>
+      </c>
+      <c r="H9" s="9">
+        <f>F9+G9</f>
+        <v>86.800000000000011</v>
+      </c>
+      <c r="I9" s="10">
+        <f>RANK(H9,$H$3:$H$22,)</f>
+        <v>7</v>
+      </c>
+      <c r="J9" s="8" t="str">
+        <f>IF(H9&gt;=90,"최우수",IF(H9&gt;=80,"우수",IF(H9&lt;60,"미달","보통")))</f>
+        <v>우수</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="9">
+        <v>84</v>
+      </c>
+      <c r="D10" s="9">
+        <v>65</v>
+      </c>
+      <c r="E10" s="9">
+        <f>IF(B10="A",20,IF(B10="B",15,10))</f>
+        <v>15</v>
+      </c>
+      <c r="F10" s="9">
+        <f>E10+(C10+D10)*40%</f>
+        <v>74.599999999999994</v>
+      </c>
+      <c r="G10" s="9">
+        <f>IF(D10&gt;=C10,D10*20%,C10*10%)</f>
+        <v>8.4</v>
+      </c>
+      <c r="H10" s="9">
+        <f>F10+G10</f>
+        <v>83</v>
+      </c>
+      <c r="I10" s="10">
+        <f>RANK(H10,$H$3:$H$22,)</f>
+        <v>8</v>
+      </c>
+      <c r="J10" s="8" t="str">
+        <f>IF(H10&gt;=90,"최우수",IF(H10&gt;=80,"우수",IF(H10&lt;60,"미달","보통")))</f>
+        <v>우수</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="9">
         <v>70</v>
       </c>
-      <c r="D3">
+      <c r="D11" s="9">
         <v>73</v>
       </c>
+      <c r="E11" s="9">
+        <f>IF(B11="A",20,IF(B11="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F11" s="9">
+        <f>E11+(C11+D11)*40%</f>
+        <v>67.2</v>
+      </c>
+      <c r="G11" s="9">
+        <f>IF(D11&gt;=C11,D11*20%,C11*10%)</f>
+        <v>14.600000000000001</v>
+      </c>
+      <c r="H11" s="9">
+        <f>F11+G11</f>
+        <v>81.800000000000011</v>
+      </c>
+      <c r="I11" s="10">
+        <f>RANK(H11,$H$3:$H$22,)</f>
+        <v>9</v>
+      </c>
+      <c r="J11" s="8" t="str">
+        <f>IF(H11&gt;=90,"최우수",IF(H11&gt;=80,"우수",IF(H11&lt;60,"미달","보통")))</f>
+        <v>우수</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="9">
+        <v>57</v>
+      </c>
+      <c r="D12" s="9">
+        <v>80</v>
+      </c>
+      <c r="E12" s="9">
+        <f>IF(B12="A",20,IF(B12="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F12" s="9">
+        <f>E12+(C12+D12)*40%</f>
+        <v>64.800000000000011</v>
+      </c>
+      <c r="G12" s="9">
+        <f>IF(D12&gt;=C12,D12*20%,C12*10%)</f>
+        <v>16</v>
+      </c>
+      <c r="H12" s="9">
+        <f>F12+G12</f>
+        <v>80.800000000000011</v>
+      </c>
+      <c r="I12" s="10">
+        <f>RANK(H12,$H$3:$H$22,)</f>
+        <v>10</v>
+      </c>
+      <c r="J12" s="8" t="str">
+        <f>IF(H12&gt;=90,"최우수",IF(H12&gt;=80,"우수",IF(H12&lt;60,"미달","보통")))</f>
+        <v>우수</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="9">
+        <v>55</v>
+      </c>
+      <c r="D13" s="9">
+        <v>64</v>
+      </c>
+      <c r="E13" s="9">
+        <f>IF(B13="A",20,IF(B13="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F13" s="9">
+        <f>E13+(C13+D13)*40%</f>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="G13" s="9">
+        <f>IF(D13&gt;=C13,D13*20%,C13*10%)</f>
+        <v>12.8</v>
+      </c>
+      <c r="H13" s="9">
+        <f>F13+G13</f>
+        <v>80.399999999999991</v>
+      </c>
+      <c r="I13" s="10">
+        <f>RANK(H13,$H$3:$H$22,)</f>
+        <v>11</v>
+      </c>
+      <c r="J13" s="8" t="str">
+        <f>IF(H13&gt;=90,"최우수",IF(H13&gt;=80,"우수",IF(H13&lt;60,"미달","보통")))</f>
+        <v>우수</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="9">
+        <v>58</v>
+      </c>
+      <c r="D14" s="9">
+        <v>68</v>
+      </c>
+      <c r="E14" s="9">
+        <f>IF(B14="A",20,IF(B14="B",15,10))</f>
+        <v>15</v>
+      </c>
+      <c r="F14" s="9">
+        <f>E14+(C14+D14)*40%</f>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="G14" s="9">
+        <f>IF(D14&gt;=C14,D14*20%,C14*10%)</f>
+        <v>13.600000000000001</v>
+      </c>
+      <c r="H14" s="9">
+        <f>F14+G14</f>
+        <v>79</v>
+      </c>
+      <c r="I14" s="10">
+        <f>RANK(H14,$H$3:$H$22,)</f>
+        <v>12</v>
+      </c>
+      <c r="J14" s="8" t="str">
+        <f>IF(H14&gt;=90,"최우수",IF(H14&gt;=80,"우수",IF(H14&lt;60,"미달","보통")))</f>
+        <v>보통</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="9">
+        <v>54</v>
+      </c>
+      <c r="D15" s="9">
+        <v>60</v>
+      </c>
+      <c r="E15" s="9">
+        <f>IF(B15="A",20,IF(B15="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F15" s="9">
+        <f>E15+(C15+D15)*40%</f>
+        <v>65.599999999999994</v>
+      </c>
+      <c r="G15" s="9">
+        <f>IF(D15&gt;=C15,D15*20%,C15*10%)</f>
+        <v>12</v>
+      </c>
+      <c r="H15" s="9">
+        <f>F15+G15</f>
+        <v>77.599999999999994</v>
+      </c>
+      <c r="I15" s="10">
+        <f>RANK(H15,$H$3:$H$22,)</f>
+        <v>13</v>
+      </c>
+      <c r="J15" s="8" t="str">
+        <f>IF(H15&gt;=90,"최우수",IF(H15&gt;=80,"우수",IF(H15&lt;60,"미달","보통")))</f>
+        <v>보통</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="9">
+        <v>82</v>
+      </c>
+      <c r="D16" s="9">
+        <v>48</v>
+      </c>
+      <c r="E16" s="9">
+        <f>IF(B16="A",20,IF(B16="B",15,10))</f>
+        <v>15</v>
+      </c>
+      <c r="F16" s="9">
+        <f>E16+(C16+D16)*40%</f>
+        <v>67</v>
+      </c>
+      <c r="G16" s="9">
+        <f>IF(D16&gt;=C16,D16*20%,C16*10%)</f>
+        <v>8.2000000000000011</v>
+      </c>
+      <c r="H16" s="9">
+        <f>F16+G16</f>
+        <v>75.2</v>
+      </c>
+      <c r="I16" s="10">
+        <f>RANK(H16,$H$3:$H$22,)</f>
+        <v>14</v>
+      </c>
+      <c r="J16" s="8" t="str">
+        <f>IF(H16&gt;=90,"최우수",IF(H16&gt;=80,"우수",IF(H16&lt;60,"미달","보통")))</f>
+        <v>보통</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="9">
+        <v>45</v>
+      </c>
+      <c r="D17" s="9">
+        <v>60</v>
+      </c>
+      <c r="E17" s="9">
+        <f>IF(B17="A",20,IF(B17="B",15,10))</f>
+        <v>20</v>
+      </c>
+      <c r="F17" s="9">
+        <f>E17+(C17+D17)*40%</f>
+        <v>62</v>
+      </c>
+      <c r="G17" s="9">
+        <f>IF(D17&gt;=C17,D17*20%,C17*10%)</f>
+        <v>12</v>
+      </c>
+      <c r="H17" s="9">
+        <f>F17+G17</f>
+        <v>74</v>
+      </c>
+      <c r="I17" s="10">
+        <f>RANK(H17,$H$3:$H$22,)</f>
+        <v>15</v>
+      </c>
+      <c r="J17" s="8" t="str">
+        <f>IF(H17&gt;=90,"최우수",IF(H17&gt;=80,"우수",IF(H17&lt;60,"미달","보통")))</f>
+        <v>보통</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="9">
+        <v>76</v>
+      </c>
+      <c r="D18" s="9">
+        <v>60</v>
+      </c>
+      <c r="E18" s="9">
+        <f>IF(B18="A",20,IF(B18="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F18" s="9">
+        <f>E18+(C18+D18)*40%</f>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="G18" s="9">
+        <f>IF(D18&gt;=C18,D18*20%,C18*10%)</f>
+        <v>7.6000000000000005</v>
+      </c>
+      <c r="H18" s="9">
+        <f>F18+G18</f>
+        <v>72</v>
+      </c>
+      <c r="I18" s="10">
+        <f>RANK(H18,$H$3:$H$22,)</f>
+        <v>16</v>
+      </c>
+      <c r="J18" s="8" t="str">
+        <f>IF(H18&gt;=90,"최우수",IF(H18&gt;=80,"우수",IF(H18&lt;60,"미달","보통")))</f>
+        <v>보통</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="9">
+        <v>54</v>
+      </c>
+      <c r="D19" s="9">
+        <v>58</v>
+      </c>
+      <c r="E19" s="9">
+        <f>IF(B19="A",20,IF(B19="B",15,10))</f>
+        <v>15</v>
+      </c>
+      <c r="F19" s="9">
+        <f>E19+(C19+D19)*40%</f>
+        <v>59.800000000000004</v>
+      </c>
+      <c r="G19" s="9">
+        <f>IF(D19&gt;=C19,D19*20%,C19*10%)</f>
+        <v>11.600000000000001</v>
+      </c>
+      <c r="H19" s="9">
+        <f>F19+G19</f>
+        <v>71.400000000000006</v>
+      </c>
+      <c r="I19" s="10">
+        <f>RANK(H19,$H$3:$H$22,)</f>
+        <v>17</v>
+      </c>
+      <c r="J19" s="8" t="str">
+        <f>IF(H19&gt;=90,"최우수",IF(H19&gt;=80,"우수",IF(H19&lt;60,"미달","보통")))</f>
+        <v>보통</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="9">
+        <v>48</v>
+      </c>
+      <c r="D20" s="9">
+        <v>50</v>
+      </c>
+      <c r="E20" s="9">
+        <f>IF(B20="A",20,IF(B20="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F20" s="9">
+        <f>E20+(C20+D20)*40%</f>
+        <v>49.2</v>
+      </c>
+      <c r="G20" s="9">
+        <f>IF(D20&gt;=C20,D20*20%,C20*10%)</f>
+        <v>10</v>
+      </c>
+      <c r="H20" s="9">
+        <f>F20+G20</f>
+        <v>59.2</v>
+      </c>
+      <c r="I20" s="10">
+        <f>RANK(H20,$H$3:$H$22,)</f>
+        <v>18</v>
+      </c>
+      <c r="J20" s="8" t="str">
+        <f>IF(H20&gt;=90,"최우수",IF(H20&gt;=80,"우수",IF(H20&lt;60,"미달","보통")))</f>
+        <v>미달</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="9">
+        <v>50</v>
+      </c>
+      <c r="D21" s="9">
+        <v>45</v>
+      </c>
+      <c r="E21" s="9">
+        <f>IF(B21="A",20,IF(B21="B",15,10))</f>
+        <v>15</v>
+      </c>
+      <c r="F21" s="9">
+        <f>E21+(C21+D21)*40%</f>
+        <v>53</v>
+      </c>
+      <c r="G21" s="9">
+        <f>IF(D21&gt;=C21,D21*20%,C21*10%)</f>
+        <v>5</v>
+      </c>
+      <c r="H21" s="9">
+        <f>F21+G21</f>
+        <v>58</v>
+      </c>
+      <c r="I21" s="10">
+        <f>RANK(H21,$H$3:$H$22,)</f>
+        <v>19</v>
+      </c>
+      <c r="J21" s="8" t="str">
+        <f>IF(H21&gt;=90,"최우수",IF(H21&gt;=80,"우수",IF(H21&lt;60,"미달","보통")))</f>
+        <v>미달</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B22" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C4">
+      <c r="C22" s="12">
         <v>50</v>
       </c>
-      <c r="D4">
+      <c r="D22" s="12">
         <v>49</v>
       </c>
+      <c r="E22" s="12">
+        <f>IF(B22="A",20,IF(B22="B",15,10))</f>
+        <v>10</v>
+      </c>
+      <c r="F22" s="12">
+        <f>E22+(C22+D22)*40%</f>
+        <v>49.6</v>
+      </c>
+      <c r="G22" s="12">
+        <f>IF(D22&gt;=C22,D22*20%,C22*10%)</f>
+        <v>5</v>
+      </c>
+      <c r="H22" s="12">
+        <f>F22+G22</f>
+        <v>54.6</v>
+      </c>
+      <c r="I22" s="13">
+        <f>RANK(H22,$H$3:$H$22,)</f>
+        <v>20</v>
+      </c>
+      <c r="J22" s="11" t="str">
+        <f>IF(H22&gt;=90,"최우수",IF(H22&gt;=80,"우수",IF(H22&lt;60,"미달","보통")))</f>
+        <v>미달</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5">
-        <v>45</v>
-      </c>
-      <c r="D5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>69</v>
-      </c>
-      <c r="D6">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>54</v>
-      </c>
-      <c r="D7">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>77</v>
-      </c>
-      <c r="D8">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>85</v>
-      </c>
-      <c r="D9">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>84</v>
-      </c>
-      <c r="D10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11">
-        <v>57</v>
-      </c>
-      <c r="D11">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12">
-        <v>48</v>
-      </c>
-      <c r="D12">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13">
-        <v>58</v>
-      </c>
-      <c r="D13">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14">
-        <v>70</v>
-      </c>
-      <c r="D14">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15">
-        <v>62</v>
-      </c>
-      <c r="D15">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16">
-        <v>65</v>
-      </c>
-      <c r="D16">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17">
-        <v>62</v>
-      </c>
-      <c r="D17">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18">
-        <v>82</v>
-      </c>
-      <c r="D18">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>55</v>
-      </c>
-      <c r="D19">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20">
-        <v>76</v>
-      </c>
-      <c r="D20">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21">
-        <v>54</v>
-      </c>
-      <c r="D21">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22">
-        <v>50</v>
-      </c>
-      <c r="D22">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="1"/>
+      <c r="C23" s="4">
+        <f>AVERAGE(C3:C22)</f>
+        <v>63.65</v>
+      </c>
+      <c r="D23" s="4">
+        <f t="shared" ref="D23:H23" si="0">AVERAGE(D3:D22)</f>
+        <v>67.3</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" si="0"/>
+        <v>67.380000000000024</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="0"/>
+        <v>12.184999999999999</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" si="0"/>
+        <v>79.565000000000012</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>35</v>
       </c>
@@ -901,8 +2799,14 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
+      <c r="H24" s="4">
+        <f>COUNTIF(H3:H22,"&gt;=85")</f>
+        <v>7</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -912,9 +2816,17 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
+      <c r="H25" s="4" cm="1">
+        <f t="array" ref="H25">ROUND(SUMPRODUCT((B3:B22="A")+(B3:B22="B"),H3:H22),0)</f>
+        <v>1069</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" s="1"/>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -925,7 +2837,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
@@ -934,8 +2846,18 @@
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
+      <c r="G27" s="4">
+        <f>SUMIFS(G3:G22,$I$3:$I$22,"&gt;=10",$I$3:$I$22,"&lt;=15")</f>
+        <v>74.600000000000009</v>
+      </c>
+      <c r="H27" s="4">
+        <f>SUMIFS(H3:H22,$I$3:$I$22,"&gt;=10",$I$3:$I$22,"&lt;=15")</f>
+        <v>466.99999999999994</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -944,9 +2866,21 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
+      <c r="G28" s="4" cm="1">
+        <f t="array" ref="G28">SUMPRODUCT((LEFT($A$3:$A$22)="이")*(($B$3:$B$22="B")+($B$3:$B$22="C")),G3:G22)</f>
+        <v>24.4</v>
+      </c>
+      <c r="H28" s="4" cm="1">
+        <f t="array" ref="H28">SUMPRODUCT((LEFT($A$3:$A$22)="이")*(($B$3:$B$22="B")+($B$3:$B$22="C")),H3:H22)</f>
+        <v>163.80000000000001</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" s="1"/>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -958,7 +2892,11 @@
       <c r="J29" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:J22">
+    <sortCondition descending="1" ref="H3:H22"/>
+    <sortCondition ref="B3:B22"/>
+  </sortState>
+  <mergeCells count="10">
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:J29"/>
@@ -967,8 +2905,13 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A26:J26"/>
+    <mergeCell ref="I23:J25"/>
+    <mergeCell ref="I27:J28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="2.3622047244094491" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>